--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129737839</v>
       </c>
       <c r="B2" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129737795</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>129737776</v>
       </c>
       <c r="B4" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,6 +991,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129773290</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 56336, Fälgaren, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>583495</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6401531</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Undersidan av granlåga med bark kvar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -675,38 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129737839</v>
+        <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>96365</v>
+        <v>91609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583487</v>
+        <v>583630</v>
       </c>
       <c r="R2" t="n">
-        <v>6401569</v>
+        <v>6401513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,45 +784,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129737795</v>
+        <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>91609</v>
+        <v>96365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583630</v>
+        <v>583615</v>
       </c>
       <c r="R3" t="n">
-        <v>6401513</v>
+        <v>6401523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +859,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>7-8 mkt stora kuddar!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,38 +891,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129737776</v>
+        <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>96365</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583615</v>
+        <v>583495</v>
       </c>
       <c r="R4" t="n">
-        <v>6401523</v>
+        <v>6401531</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7-8 mkt stora kuddar!</t>
+          <t>Undersidan av granlåga med bark kvar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,45 +1005,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129773290</v>
+        <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>96370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583495</v>
+        <v>583487</v>
       </c>
       <c r="R5" t="n">
-        <v>6401531</v>
+        <v>6401569</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Undersidan av granlåga med bark kvar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737795</v>
       </c>
       <c r="B2" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129773290</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129737839</v>
       </c>
       <c r="B5" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56336-2025 artfynd.xlsx
+++ b/artfynd/A 56336-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129737795</v>
+        <v>129773290</v>
       </c>
       <c r="B2" t="n">
-        <v>91659</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583630</v>
+        <v>583495</v>
       </c>
       <c r="R2" t="n">
-        <v>6401513</v>
+        <v>6401531</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Undersidan av granlåga med bark kvar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
         <v>129737776</v>
       </c>
       <c r="B3" t="n">
-        <v>96426</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,45 +896,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773290</v>
+        <v>129737839</v>
       </c>
       <c r="B4" t="n">
-        <v>91639</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583495</v>
+        <v>583487</v>
       </c>
       <c r="R4" t="n">
-        <v>6401531</v>
+        <v>6401569</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,11 +971,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Undersidan av granlåga med bark kvar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,38 +998,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129737839</v>
+        <v>129737795</v>
       </c>
       <c r="B5" t="n">
-        <v>96427</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583487</v>
+        <v>583630</v>
       </c>
       <c r="R5" t="n">
-        <v>6401569</v>
+        <v>6401513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
